--- a/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
@@ -766,10 +766,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -821,22 +821,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -983,22 +983,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -1092,22 +1092,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -1314,22 +1314,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1431,22 +1431,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>04/21/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>ILWU PMA COASTWISE</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Medicare Railroad (RR Medicare MetraHealth) 00882</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>ILWU PMA COASTWISE</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>04/21/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -1554,22 +1554,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>04/21/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>ILWU PMA COASTWISE</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Medicare Railroad (RR Medicare MetraHealth) 00882</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>ILWU PMA COASTWISE</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>04/21/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1673,22 +1673,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1790,22 +1790,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1907,22 +1907,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>04/15/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>04/15/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2016,22 +2016,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>04/15/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>04/15/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2125,22 +2125,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -2359,22 +2359,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>04/22/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>04/22/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -2476,22 +2476,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>04/22/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>04/22/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -2597,22 +2597,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>04/23/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>ChampVA - HAC</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>ChampVA - HAC</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>04/23/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -2716,22 +2716,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>04/24/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>04/24/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2829,22 +2829,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>04/24/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>04/24/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -2942,22 +2942,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>04/15/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>04/15/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -3049,22 +3049,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>04/29/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>04/29/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -3156,22 +3156,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>04/29/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>04/29/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -3292,10 +3292,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -3347,22 +3347,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -3509,22 +3509,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -3634,22 +3634,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>04/02/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -3759,22 +3759,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>04/09/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -3872,22 +3872,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -3989,22 +3989,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -4106,22 +4106,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Continental Benefits</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -4227,22 +4227,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>04/14/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>04/14/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -4344,22 +4344,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -4461,22 +4461,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -4578,22 +4578,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>04/27/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>04/27/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Mutual of Omaha Insurance Company</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -4816,22 +4816,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>04/29/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Medical Associates Health Plan</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Medical Associates Health Plan</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>04/29/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -4943,22 +4943,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>04/30/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>04/30/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -5066,22 +5066,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -5183,22 +5183,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -5300,22 +5300,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>04/09/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -5421,22 +5421,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>04/10/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>04/10/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -5538,22 +5538,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -5663,22 +5663,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -5784,22 +5784,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -5905,22 +5905,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>04/16/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>04/16/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -6026,22 +6026,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>04/16/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>04/16/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -6143,22 +6143,22 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>04/16/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>04/16/2026</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -6264,22 +6264,22 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -6385,22 +6385,22 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>04/23/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>04/23/2026</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -6498,22 +6498,22 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>04/23/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>04/23/2026</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -6611,22 +6611,22 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>04/27/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>04/27/2026</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -6732,22 +6732,22 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>04/27/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>04/27/2026</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -6853,22 +6853,22 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>LIEN 05</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -6978,22 +6978,22 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
+          <t>04/30/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>04/30/2026</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -7099,22 +7099,22 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
+          <t>04/30/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>04/30/2026</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -7228,22 +7228,22 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
           <t>AMBETTER</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>AMBETTER</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>04/02/2026</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -7349,22 +7349,22 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
+          <t>04/21/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>04/21/2026</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -7468,22 +7468,22 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
+          <t>04/21/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>04/21/2026</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -7608,10 +7608,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -7663,22 +7663,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -7825,22 +7825,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Health Choice Arizona</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Health Choice Arizona</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -7962,22 +7962,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Health Choice Arizona</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Health Choice Arizona</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -8091,22 +8091,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Health Choice Arizona</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Health Choice Arizona</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -8224,22 +8224,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -8345,22 +8345,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -8599,22 +8599,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -8724,22 +8724,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -8857,22 +8857,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -8986,22 +8986,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -9111,22 +9111,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -9240,22 +9240,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -9377,22 +9377,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -9510,22 +9510,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -9639,22 +9639,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -9889,22 +9889,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -10018,22 +10018,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -10151,22 +10151,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -10276,22 +10276,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -10401,22 +10401,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -10530,22 +10530,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -10659,22 +10659,22 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -10792,22 +10792,22 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -10925,22 +10925,22 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -11064,22 +11064,22 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -11203,22 +11203,22 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -11338,22 +11338,22 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -11473,22 +11473,22 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -11608,22 +11608,22 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -11739,22 +11739,22 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -11882,22 +11882,22 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -12017,22 +12017,22 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -12148,22 +12148,22 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -12279,22 +12279,22 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -12398,22 +12398,22 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -12525,22 +12525,22 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -12652,22 +12652,22 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -12804,10 +12804,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -12859,22 +12859,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -13021,22 +13021,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Tricare for Life (All Regions)</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -13138,22 +13138,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Physicians Mutual Insurance Company - ENS</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -13255,22 +13255,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>04/16/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>04/16/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -13368,22 +13368,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>04/20/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -13485,22 +13485,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>04/23/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>04/23/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -13606,22 +13606,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -13727,22 +13727,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -13844,22 +13844,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -13957,22 +13957,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -14074,22 +14074,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -14199,22 +14199,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -14316,22 +14316,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -14441,22 +14441,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -14566,22 +14566,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>04/15/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>04/15/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -14687,22 +14687,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>04/15/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>04/15/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -14808,22 +14808,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>04/15/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>04/15/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -14925,22 +14925,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>04/15/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>04/15/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -15042,22 +15042,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>04/16/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>04/16/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -15159,22 +15159,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>04/17/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>04/17/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -15272,22 +15272,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>04/17/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>04/17/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -15385,22 +15385,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>04/23/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>04/23/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -15506,22 +15506,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>04/23/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>04/23/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -15627,22 +15627,22 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>04/23/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>04/23/2026</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -15752,22 +15752,22 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>04/23/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>04/23/2026</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -15877,22 +15877,22 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>04/27/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>04/27/2026</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -15998,22 +15998,22 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>04/27/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>04/27/2026</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>04/29/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>04/29/2026</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -16244,22 +16244,22 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>04/29/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>04/29/2026</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -16365,22 +16365,22 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>04/29/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>04/29/2026</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -16486,22 +16486,22 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
+          <t>04/29/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>04/29/2026</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -16607,22 +16607,22 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -16732,22 +16732,22 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -16861,22 +16861,22 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -16986,22 +16986,22 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -17111,22 +17111,22 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
+          <t>04/03/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -17228,22 +17228,22 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
           <t>Imperial Insurance Companies Inc Exchange AZ (IEXAZ) (WAYSTAR ONLY)</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Imperial Insurance Companies Inc Exchange AZ (IEXAZ) (WAYSTAR ONLY)</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -17351,22 +17351,22 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
+          <t>04/13/2026</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
           <t>Imperial Insurance Companies Inc Exchange AZ (IEXAZ) (WAYSTAR ONLY)</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Imperial Insurance Companies Inc Exchange AZ (IEXAZ) (WAYSTAR ONLY)</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -17470,22 +17470,22 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
+          <t>04/15/2026</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
           <t>AFSAT MEDICAL PLAN</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>AFSAT MEDICAL PLAN</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>04/15/2026</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -17589,22 +17589,22 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
+          <t>04/15/2026</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
           <t>AFSAT MEDICAL PLAN</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>AFSAT MEDICAL PLAN</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>04/15/2026</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -17737,10 +17737,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -17792,22 +17792,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -17962,22 +17962,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>04/14/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>04/14/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -18079,22 +18079,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -18204,22 +18204,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>04/29/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Banner Aetna</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Banner Aetna</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>04/29/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -18321,22 +18321,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>04/30/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>AMBETTER</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>AMBETTER</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>04/30/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -18438,22 +18438,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>USAA Life Insurance Company</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>USAA Life Insurance Company</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>04/07/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -18561,22 +18561,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Physicians Mutual Insurance Company - ENS</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -18678,22 +18678,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Physicians Mutual Insurance Company - ENS</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -18795,22 +18795,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Physicians Mutual Insurance Company - ENS</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -18916,22 +18916,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>04/15/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>AARP United Healthcare</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>04/15/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -19039,22 +19039,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>04/21/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>04/21/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -19166,22 +19166,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>04/21/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>04/21/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -19293,22 +19293,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>04/21/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>04/21/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -19420,22 +19420,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>04/22/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>04/22/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -19543,22 +19543,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Aetna Senior Supplemental (AESSI) - Secondary Only 62118</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -19656,22 +19656,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Aetna Senior Supplemental (AESSI) - Secondary Only 62118</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -19769,22 +19769,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Aetna Senior Supplemental (AESSI) - Secondary Only 62118</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -19882,22 +19882,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>04/29/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>04/29/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -19995,22 +19995,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>04/29/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>04/29/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -20108,22 +20108,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>04/29/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>04/29/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -20221,22 +20221,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>04/02/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -20342,22 +20342,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>04/02/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -20463,22 +20463,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>04/07/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -20580,22 +20580,22 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>04/07/2026</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -20697,22 +20697,22 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>04/09/2026</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -20814,22 +20814,22 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>Mercy Care RBHA</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>04/09/2026</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -20927,22 +20927,22 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Mercy Care RBHA</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>04/09/2026</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -21040,22 +21040,22 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Mercy Care RBHA</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>04/09/2026</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -21157,22 +21157,22 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>04/23/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>04/23/2026</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -21278,22 +21278,22 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>04/23/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>04/23/2026</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -21395,22 +21395,22 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
+          <t>04/23/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>04/23/2026</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -21508,22 +21508,22 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
+          <t>04/23/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>04/23/2026</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -21625,22 +21625,22 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
+          <t>04/30/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>04/30/2026</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -21740,22 +21740,22 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
+          <t>04/30/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>04/30/2026</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -21861,22 +21861,22 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
           <t>Banner Medicare Advantage Prime HMO (BMAH)</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Banner Medicare Advantage Prime HMO (BMAH)</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -21986,22 +21986,22 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
           <t>Banner Medicare Advantage Prime HMO (BMAH)</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Banner Medicare Advantage Prime HMO (BMAH)</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -22111,22 +22111,22 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
           <t>Banner Medicare Advantage Prime HMO (BMAH)</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Banner Medicare Advantage Prime HMO (BMAH)</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>04/01/2026</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -22236,22 +22236,22 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
+          <t>04/22/2026</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>04/22/2026</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">

--- a/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
@@ -1041,26 +1041,26 @@
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="5" t="n">
-        <v>555379100</v>
+        <v>554943318</v>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>HF549150041</t>
+          <t>HF534535040</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K2" s="4" t="n"/>
@@ -1079,16 +1079,16 @@
         <v/>
       </c>
       <c r="M2" s="7" t="n">
-        <v>46300</v>
+        <v>46478</v>
       </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
-          <t>180 days</t>
+          <t>365 days</t>
         </is>
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
-          <t>VETERANS ADMIN (VA CCN)</t>
+          <t>MEDICARE</t>
         </is>
       </c>
       <c r="P2" s="6" t="n"/>
@@ -1098,7 +1098,7 @@
         <v>1</v>
       </c>
       <c r="T2" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U2" s="8" t="n">
         <v>0</v>
@@ -1106,16 +1106,20 @@
       <c r="V2" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W2" s="6" t="n"/>
+      <c r="W2" s="6" t="inlineStr">
+        <is>
+          <t>05/15/2026</t>
+        </is>
+      </c>
       <c r="X2" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="Y2" s="5" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="Z2" s="6" t="inlineStr">
         <is>
-          <t>F39</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA2" s="6" t="n"/>
@@ -1124,12 +1128,12 @@
       <c r="AD2" s="5" t="n"/>
       <c r="AE2" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>MEARS, CHAD</t>
         </is>
       </c>
       <c r="AF2" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG2" s="6" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="AI2" s="9" t="n"/>
       <c r="AJ2" s="5" t="n">
-        <v>777</v>
+        <v>660</v>
       </c>
     </row>
     <row r="3">
@@ -1152,26 +1156,26 @@
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="4" t="n"/>
       <c r="D3" s="5" t="n">
-        <v>555379100</v>
+        <v>554943318</v>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>HF549150041</t>
+          <t>HF534535040</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
@@ -1181,7 +1185,7 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K3" s="4" t="n"/>
@@ -1190,16 +1194,16 @@
         <v/>
       </c>
       <c r="M3" s="7" t="n">
-        <v>46300</v>
+        <v>46478</v>
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>180 days</t>
+          <t>365 days</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>VETERANS ADMIN (VA CCN)</t>
+          <t>MEDICARE</t>
         </is>
       </c>
       <c r="P3" s="6" t="n"/>
@@ -1209,7 +1213,7 @@
         <v>1</v>
       </c>
       <c r="T3" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U3" s="8" t="n">
         <v>0</v>
@@ -1217,16 +1221,20 @@
       <c r="V3" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W3" s="6" t="n"/>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>05/15/2026</t>
+        </is>
+      </c>
       <c r="X3" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="Z3" s="6" t="inlineStr">
         <is>
-          <t>F39</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA3" s="6" t="n"/>
@@ -1235,12 +1243,12 @@
       <c r="AD3" s="5" t="n"/>
       <c r="AE3" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>MEARS, CHAD</t>
         </is>
       </c>
       <c r="AF3" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG3" s="6" t="inlineStr">
@@ -1255,44 +1263,48 @@
       </c>
       <c r="AI3" s="9" t="n"/>
       <c r="AJ3" s="5" t="n">
-        <v>778</v>
+        <v>712</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="5" t="n">
-        <v>554943318</v>
+        <v>556872696</v>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>HF534535040</t>
+          <t>HF505008638</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>ILWU PMA COASTWISE</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>Medicare Railroad (RR Medicare MetraHealth) 00882</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>ILWU PMA COASTWISE</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K4" s="4" t="n"/>
@@ -1301,7 +1313,7 @@
         <v/>
       </c>
       <c r="M4" s="7" t="n">
-        <v>46478</v>
+        <v>46498</v>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
@@ -1320,24 +1332,24 @@
         <v>1</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>0</v>
+        <v>875.72</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>0</v>
+        <v>122.91</v>
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
-          <t>05/15/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="X4" s="8" t="n">
-        <v>396.27</v>
+        <v>31.35</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="Z4" s="6" t="inlineStr">
         <is>
@@ -1347,15 +1359,17 @@
       <c r="AA4" s="6" t="n"/>
       <c r="AB4" s="6" t="n"/>
       <c r="AC4" s="6" t="n"/>
-      <c r="AD4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n">
+        <v>561534353</v>
+      </c>
       <c r="AE4" s="6" t="inlineStr">
         <is>
-          <t>MEARS, CHAD</t>
+          <t>SARKAR, AWNIK</t>
         </is>
       </c>
       <c r="AF4" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG4" s="6" t="inlineStr">
@@ -1368,46 +1382,54 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI4" s="9" t="n"/>
+      <c r="AI4" s="9" t="inlineStr">
+        <is>
+          <t>Railroad Medicare - same statutory 1 year Medicare limit.</t>
+        </is>
+      </c>
       <c r="AJ4" s="5" t="n">
-        <v>660</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="5" t="n">
-        <v>554943318</v>
+        <v>556872696</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>HF534535040</t>
+          <t>HF505008638</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>ILWU PMA COASTWISE</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>Medicare Railroad (RR Medicare MetraHealth) 00882</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>ILWU PMA COASTWISE</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K5" s="4" t="n"/>
@@ -1416,7 +1438,7 @@
         <v/>
       </c>
       <c r="M5" s="7" t="n">
-        <v>46478</v>
+        <v>46498</v>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
@@ -1435,24 +1457,24 @@
         <v>1</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>0</v>
+        <v>337.05</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>0</v>
+        <v>47.18</v>
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
-          <t>05/15/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="X5" s="8" t="n">
-        <v>976.64</v>
+        <v>12.04</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="Z5" s="6" t="inlineStr">
         <is>
@@ -1462,15 +1484,17 @@
       <c r="AA5" s="6" t="n"/>
       <c r="AB5" s="6" t="n"/>
       <c r="AC5" s="6" t="n"/>
-      <c r="AD5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n">
+        <v>561534353</v>
+      </c>
       <c r="AE5" s="6" t="inlineStr">
         <is>
-          <t>MEARS, CHAD</t>
+          <t>SARKAR, AWNIK</t>
         </is>
       </c>
       <c r="AF5" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG5" s="6" t="inlineStr">
@@ -1483,50 +1507,50 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI5" s="9" t="n"/>
+      <c r="AI5" s="9" t="inlineStr">
+        <is>
+          <t>Railroad Medicare - same statutory 1 year Medicare limit.</t>
+        </is>
+      </c>
       <c r="AJ5" s="5" t="n">
-        <v>712</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="5" t="n">
-        <v>556872696</v>
+        <v>566720408</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>HF505008638</t>
+          <t>HF537685966</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>ILWU PMA COASTWISE</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Medicare Railroad (RR Medicare MetraHealth) 00882</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>ILWU PMA COASTWISE</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K6" s="4" t="n"/>
@@ -1535,16 +1559,16 @@
         <v/>
       </c>
       <c r="M6" s="7" t="n">
-        <v>46498</v>
+        <v>46203</v>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>365 days</t>
+          <t>90 days</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>MEDICARE</t>
+          <t>BCBS</t>
         </is>
       </c>
       <c r="P6" s="6" t="n"/>
@@ -1554,44 +1578,42 @@
         <v>1</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>875.72</v>
+        <v>0</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>122.91</v>
+        <v>0</v>
       </c>
       <c r="W6" s="6" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>05/20/2026</t>
         </is>
       </c>
       <c r="X6" s="8" t="n">
-        <v>31.35</v>
+        <v>396.27</v>
       </c>
       <c r="Y6" s="5" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="Z6" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F330</t>
         </is>
       </c>
       <c r="AA6" s="6" t="n"/>
       <c r="AB6" s="6" t="n"/>
       <c r="AC6" s="6" t="n"/>
-      <c r="AD6" s="5" t="n">
-        <v>561534353</v>
-      </c>
+      <c r="AD6" s="5" t="n"/>
       <c r="AE6" s="6" t="inlineStr">
         <is>
-          <t>SARKAR, AWNIK</t>
+          <t>BAUGHER, TIMOTHY</t>
         </is>
       </c>
       <c r="AF6" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG6" s="6" t="inlineStr">
@@ -1606,52 +1628,48 @@
       </c>
       <c r="AI6" s="9" t="inlineStr">
         <is>
-          <t>Railroad Medicare - same statutory 1 year Medicare limit.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ6" s="5" t="n">
-        <v>156</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="n"/>
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="5" t="n">
-        <v>556872696</v>
+        <v>566720408</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>HF505008638</t>
+          <t>HF537685966</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>ILWU PMA COASTWISE</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Medicare Railroad (RR Medicare MetraHealth) 00882</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>ILWU PMA COASTWISE</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K7" s="4" t="n"/>
@@ -1660,16 +1678,16 @@
         <v/>
       </c>
       <c r="M7" s="7" t="n">
-        <v>46498</v>
+        <v>46203</v>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>365 days</t>
+          <t>90 days</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>MEDICARE</t>
+          <t>BCBS</t>
         </is>
       </c>
       <c r="P7" s="6" t="n"/>
@@ -1679,44 +1697,42 @@
         <v>1</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>337.05</v>
+        <v>0</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>47.18</v>
+        <v>0</v>
       </c>
       <c r="W7" s="6" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>05/20/2026</t>
         </is>
       </c>
       <c r="X7" s="8" t="n">
-        <v>12.04</v>
+        <v>976.64</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="Z7" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F330</t>
         </is>
       </c>
       <c r="AA7" s="6" t="n"/>
       <c r="AB7" s="6" t="n"/>
       <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="5" t="n">
-        <v>561534353</v>
-      </c>
+      <c r="AD7" s="5" t="n"/>
       <c r="AE7" s="6" t="inlineStr">
         <is>
-          <t>SARKAR, AWNIK</t>
+          <t>BAUGHER, TIMOTHY</t>
         </is>
       </c>
       <c r="AF7" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG7" s="6" t="inlineStr">
@@ -1731,11 +1747,11 @@
       </c>
       <c r="AI7" s="9" t="inlineStr">
         <is>
-          <t>Railroad Medicare - same statutory 1 year Medicare limit.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ7" s="5" t="n">
-        <v>157</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8">
@@ -1743,31 +1759,31 @@
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="5" t="n">
-        <v>566720408</v>
+        <v>556413148</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>HF537685966</t>
+          <t>HF509386349</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>04/15/2026</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
@@ -1781,7 +1797,7 @@
         <v/>
       </c>
       <c r="M8" s="7" t="n">
-        <v>46203</v>
+        <v>46217</v>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
@@ -1790,17 +1806,17 @@
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>BCBS</t>
+          <t>OPTUM</t>
         </is>
       </c>
       <c r="P8" s="6" t="n"/>
       <c r="Q8" s="6" t="n"/>
       <c r="R8" s="6" t="n"/>
       <c r="S8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>396.27</v>
+        <v>792.54</v>
       </c>
       <c r="U8" s="8" t="n">
         <v>0</v>
@@ -1808,20 +1824,16 @@
       <c r="V8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="6" t="inlineStr">
-        <is>
-          <t>05/20/2026</t>
-        </is>
-      </c>
+      <c r="W8" s="6" t="n"/>
       <c r="X8" s="8" t="n">
-        <v>396.27</v>
+        <v>792.54</v>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="Z8" s="6" t="inlineStr">
         <is>
-          <t>F330</t>
+          <t>F1190</t>
         </is>
       </c>
       <c r="AA8" s="6" t="n"/>
@@ -1830,12 +1842,12 @@
       <c r="AD8" s="5" t="n"/>
       <c r="AE8" s="6" t="inlineStr">
         <is>
-          <t>BAUGHER, TIMOTHY</t>
+          <t>O'NEIL, ROY</t>
         </is>
       </c>
       <c r="AF8" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG8" s="6" t="inlineStr">
@@ -1848,13 +1860,9 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI8" s="9" t="inlineStr">
-        <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
-        </is>
-      </c>
+      <c r="AI8" s="9" t="n"/>
       <c r="AJ8" s="5" t="n">
-        <v>213</v>
+        <v>953</v>
       </c>
     </row>
     <row r="9">
@@ -1862,31 +1870,31 @@
       <c r="B9" s="3" t="n"/>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="5" t="n">
-        <v>566720408</v>
+        <v>556413148</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>HF537685966</t>
+          <t>HF509386349</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>04/15/2026</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
@@ -1900,7 +1908,7 @@
         <v/>
       </c>
       <c r="M9" s="7" t="n">
-        <v>46203</v>
+        <v>46217</v>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
@@ -1909,7 +1917,7 @@
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>BCBS</t>
+          <t>OPTUM</t>
         </is>
       </c>
       <c r="P9" s="6" t="n"/>
@@ -1927,20 +1935,16 @@
       <c r="V9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W9" s="6" t="inlineStr">
-        <is>
-          <t>05/20/2026</t>
-        </is>
-      </c>
+      <c r="W9" s="6" t="n"/>
       <c r="X9" s="8" t="n">
         <v>976.64</v>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="Z9" s="6" t="inlineStr">
         <is>
-          <t>F330</t>
+          <t>F1190</t>
         </is>
       </c>
       <c r="AA9" s="6" t="n"/>
@@ -1949,12 +1953,12 @@
       <c r="AD9" s="5" t="n"/>
       <c r="AE9" s="6" t="inlineStr">
         <is>
-          <t>BAUGHER, TIMOTHY</t>
+          <t>O'NEIL, ROY</t>
         </is>
       </c>
       <c r="AF9" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG9" s="6" t="inlineStr">
@@ -1967,13 +1971,9 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI9" s="9" t="inlineStr">
-        <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
-        </is>
-      </c>
+      <c r="AI9" s="9" t="n"/>
       <c r="AJ9" s="5" t="n">
-        <v>214</v>
+        <v>954</v>
       </c>
     </row>
     <row r="10">
@@ -1981,26 +1981,26 @@
       <c r="B10" s="3" t="n"/>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="5" t="n">
-        <v>556413148</v>
+        <v>556564886</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>HF509386349</t>
+          <t>HF331718997</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>04/15/2026</t>
+          <t>04/20/2026</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -2019,7 +2019,7 @@
         <v/>
       </c>
       <c r="M10" s="7" t="n">
-        <v>46217</v>
+        <v>46222</v>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
@@ -2028,17 +2028,17 @@
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>OPTUM</t>
+          <t>BCBS</t>
         </is>
       </c>
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
       <c r="R10" s="6" t="n"/>
       <c r="S10" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>792.54</v>
+        <v>396.27</v>
       </c>
       <c r="U10" s="8" t="n">
         <v>0</v>
@@ -2046,16 +2046,20 @@
       <c r="V10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W10" s="6" t="n"/>
+      <c r="W10" s="6" t="inlineStr">
+        <is>
+          <t>05/15/2026</t>
+        </is>
+      </c>
       <c r="X10" s="8" t="n">
-        <v>792.54</v>
+        <v>396.27</v>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="Z10" s="6" t="inlineStr">
         <is>
-          <t>F1190</t>
+          <t>F4323</t>
         </is>
       </c>
       <c r="AA10" s="6" t="n"/>
@@ -2064,12 +2068,12 @@
       <c r="AD10" s="5" t="n"/>
       <c r="AE10" s="6" t="inlineStr">
         <is>
-          <t>O'NEIL, ROY</t>
+          <t>SARKAR, AWNIK</t>
         </is>
       </c>
       <c r="AF10" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG10" s="6" t="inlineStr">
@@ -2082,9 +2086,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI10" s="9" t="n"/>
+      <c r="AI10" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
+        </is>
+      </c>
       <c r="AJ10" s="5" t="n">
-        <v>953</v>
+        <v>661</v>
       </c>
     </row>
     <row r="11">
@@ -2092,26 +2100,26 @@
       <c r="B11" s="3" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="5" t="n">
-        <v>556413148</v>
+        <v>556564886</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>HF509386349</t>
+          <t>HF331718997</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>04/15/2026</t>
+          <t>04/20/2026</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -2130,7 +2138,7 @@
         <v/>
       </c>
       <c r="M11" s="7" t="n">
-        <v>46217</v>
+        <v>46222</v>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
@@ -2139,7 +2147,7 @@
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>OPTUM</t>
+          <t>BCBS</t>
         </is>
       </c>
       <c r="P11" s="6" t="n"/>
@@ -2157,16 +2165,20 @@
       <c r="V11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W11" s="6" t="n"/>
+      <c r="W11" s="6" t="inlineStr">
+        <is>
+          <t>05/15/2026</t>
+        </is>
+      </c>
       <c r="X11" s="8" t="n">
         <v>976.64</v>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="Z11" s="6" t="inlineStr">
         <is>
-          <t>F1190</t>
+          <t>F4323</t>
         </is>
       </c>
       <c r="AA11" s="6" t="n"/>
@@ -2175,12 +2187,12 @@
       <c r="AD11" s="5" t="n"/>
       <c r="AE11" s="6" t="inlineStr">
         <is>
-          <t>O'NEIL, ROY</t>
+          <t>SARKAR, AWNIK</t>
         </is>
       </c>
       <c r="AF11" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG11" s="6" t="inlineStr">
@@ -2193,9 +2205,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI11" s="9" t="n"/>
+      <c r="AI11" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
+        </is>
+      </c>
       <c r="AJ11" s="5" t="n">
-        <v>954</v>
+        <v>662</v>
       </c>
     </row>
     <row r="12">
@@ -2203,26 +2219,26 @@
       <c r="B12" s="3" t="n"/>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="5" t="n">
-        <v>556564886</v>
+        <v>556918462</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>HF331718997</t>
+          <t>HF341023592</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>04/20/2026</t>
+          <t>04/22/2026</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -2241,7 +2257,7 @@
         <v/>
       </c>
       <c r="M12" s="7" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
@@ -2250,7 +2266,7 @@
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>BCBS</t>
+          <t>OPTUM</t>
         </is>
       </c>
       <c r="P12" s="6" t="n"/>
@@ -2270,32 +2286,36 @@
       </c>
       <c r="W12" s="6" t="inlineStr">
         <is>
-          <t>05/15/2026</t>
+          <t>05/25/2026</t>
         </is>
       </c>
       <c r="X12" s="8" t="n">
         <v>396.27</v>
       </c>
       <c r="Y12" s="5" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z12" s="6" t="inlineStr">
         <is>
-          <t>F4323</t>
-        </is>
-      </c>
-      <c r="AA12" s="6" t="n"/>
+          <t>F332</t>
+        </is>
+      </c>
+      <c r="AA12" s="6" t="inlineStr">
+        <is>
+          <t>F411</t>
+        </is>
+      </c>
       <c r="AB12" s="6" t="n"/>
       <c r="AC12" s="6" t="n"/>
       <c r="AD12" s="5" t="n"/>
       <c r="AE12" s="6" t="inlineStr">
         <is>
-          <t>SARKAR, AWNIK</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF12" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG12" s="6" t="inlineStr">
@@ -2308,13 +2328,9 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI12" s="9" t="inlineStr">
-        <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
-        </is>
-      </c>
+      <c r="AI12" s="9" t="n"/>
       <c r="AJ12" s="5" t="n">
-        <v>661</v>
+        <v>794</v>
       </c>
     </row>
     <row r="13">
@@ -2322,26 +2338,26 @@
       <c r="B13" s="3" t="n"/>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="5" t="n">
-        <v>556564886</v>
+        <v>556918462</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>HF331718997</t>
+          <t>HF341023592</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>04/20/2026</t>
+          <t>04/22/2026</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -2360,7 +2376,7 @@
         <v/>
       </c>
       <c r="M13" s="7" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
@@ -2369,7 +2385,7 @@
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>BCBS</t>
+          <t>OPTUM</t>
         </is>
       </c>
       <c r="P13" s="6" t="n"/>
@@ -2389,32 +2405,36 @@
       </c>
       <c r="W13" s="6" t="inlineStr">
         <is>
-          <t>05/15/2026</t>
+          <t>05/25/2026</t>
         </is>
       </c>
       <c r="X13" s="8" t="n">
         <v>976.64</v>
       </c>
       <c r="Y13" s="5" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z13" s="6" t="inlineStr">
         <is>
-          <t>F4323</t>
-        </is>
-      </c>
-      <c r="AA13" s="6" t="n"/>
+          <t>F332</t>
+        </is>
+      </c>
+      <c r="AA13" s="6" t="inlineStr">
+        <is>
+          <t>F411</t>
+        </is>
+      </c>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
       <c r="AD13" s="5" t="n"/>
       <c r="AE13" s="6" t="inlineStr">
         <is>
-          <t>SARKAR, AWNIK</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF13" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG13" s="6" t="inlineStr">
@@ -2427,50 +2447,50 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI13" s="9" t="inlineStr">
-        <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
-        </is>
-      </c>
+      <c r="AI13" s="9" t="n"/>
       <c r="AJ13" s="5" t="n">
-        <v>662</v>
+        <v>795</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
       <c r="B14" s="3" t="n"/>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="5" t="n">
-        <v>556918462</v>
+        <v>557054917</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>HF341023592</t>
+          <t>HF545223898</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>04/22/2026</t>
+          <t>04/23/2026</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>ChampVA - HAC</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>Humana Gold Plus HMO</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>ChampVA - HAC</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K14" s="4" t="n"/>
@@ -2479,7 +2499,7 @@
         <v/>
       </c>
       <c r="M14" s="7" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
@@ -2488,7 +2508,7 @@
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>OPTUM</t>
+          <t>HUMANA MA</t>
         </is>
       </c>
       <c r="P14" s="6" t="n"/>
@@ -2498,46 +2518,44 @@
         <v>1</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>0</v>
+        <v>843.88</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>0</v>
+        <v>107.76</v>
       </c>
       <c r="W14" s="6" t="inlineStr">
         <is>
-          <t>05/25/2026</t>
+          <t>05/15/2026</t>
         </is>
       </c>
       <c r="X14" s="8" t="n">
-        <v>396.27</v>
+        <v>25</v>
       </c>
       <c r="Y14" s="5" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z14" s="6" t="inlineStr">
         <is>
-          <t>F332</t>
-        </is>
-      </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>F411</t>
-        </is>
-      </c>
+          <t>F4323</t>
+        </is>
+      </c>
+      <c r="AA14" s="6" t="n"/>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
-      <c r="AD14" s="5" t="n"/>
+      <c r="AD14" s="5" t="n">
+        <v>561534406</v>
+      </c>
       <c r="AE14" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>BURGHER, ABRAM</t>
         </is>
       </c>
       <c r="AF14" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG14" s="6" t="inlineStr">
@@ -2550,9 +2568,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI14" s="9" t="n"/>
+      <c r="AI14" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
+        </is>
+      </c>
       <c r="AJ14" s="5" t="n">
-        <v>794</v>
+        <v>505</v>
       </c>
     </row>
     <row r="15">
@@ -2560,16 +2582,16 @@
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="5" t="n">
-        <v>556918462</v>
+        <v>557132196</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>HF341023592</t>
+          <t>HF460603685</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>04/22/2026</t>
+          <t>04/24/2026</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -2589,7 +2611,7 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K15" s="4" t="n"/>
@@ -2598,7 +2620,7 @@
         <v/>
       </c>
       <c r="M15" s="7" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
@@ -2617,7 +2639,7 @@
         <v>1</v>
       </c>
       <c r="T15" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U15" s="8" t="n">
         <v>0</v>
@@ -2631,27 +2653,23 @@
         </is>
       </c>
       <c r="X15" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="Y15" s="5" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Z15" s="6" t="inlineStr">
         <is>
-          <t>F332</t>
-        </is>
-      </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>F411</t>
-        </is>
-      </c>
+          <t>F4323</t>
+        </is>
+      </c>
+      <c r="AA15" s="6" t="n"/>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
       <c r="AD15" s="5" t="n"/>
       <c r="AE15" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF15" s="6" t="inlineStr">
@@ -2671,43 +2689,39 @@
       </c>
       <c r="AI15" s="9" t="n"/>
       <c r="AJ15" s="5" t="n">
-        <v>795</v>
+        <v>640</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="n"/>
       <c r="B16" s="3" t="n"/>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="5" t="n">
-        <v>557054917</v>
+        <v>557132196</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>HF545223898</t>
+          <t>HF460603685</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>04/23/2026</t>
+          <t>04/24/2026</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>ChampVA - HAC</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Humana Gold Plus HMO</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>ChampVA - HAC</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
@@ -2721,7 +2735,7 @@
         <v/>
       </c>
       <c r="M16" s="7" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
@@ -2730,7 +2744,7 @@
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>HUMANA MA</t>
+          <t>OPTUM</t>
         </is>
       </c>
       <c r="P16" s="6" t="n"/>
@@ -2743,21 +2757,21 @@
         <v>976.64</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>843.88</v>
+        <v>0</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>107.76</v>
+        <v>0</v>
       </c>
       <c r="W16" s="6" t="inlineStr">
         <is>
-          <t>05/15/2026</t>
+          <t>05/25/2026</t>
         </is>
       </c>
       <c r="X16" s="8" t="n">
-        <v>25</v>
+        <v>976.64</v>
       </c>
       <c r="Y16" s="5" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Z16" s="6" t="inlineStr">
         <is>
@@ -2767,17 +2781,15 @@
       <c r="AA16" s="6" t="n"/>
       <c r="AB16" s="6" t="n"/>
       <c r="AC16" s="6" t="n"/>
-      <c r="AD16" s="5" t="n">
-        <v>561534406</v>
-      </c>
+      <c r="AD16" s="5" t="n"/>
       <c r="AE16" s="6" t="inlineStr">
         <is>
-          <t>BURGHER, ABRAM</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF16" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG16" s="6" t="inlineStr">
@@ -2790,13 +2802,9 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI16" s="9" t="inlineStr">
-        <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
-        </is>
-      </c>
+      <c r="AI16" s="9" t="n"/>
       <c r="AJ16" s="5" t="n">
-        <v>505</v>
+        <v>674</v>
       </c>
     </row>
     <row r="17">
@@ -2804,26 +2812,26 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="5" t="n">
-        <v>557132196</v>
+        <v>555379100</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>HF460603685</t>
+          <t>HF549150041</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>04/24/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -2833,7 +2841,7 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K17" s="4" t="n"/>
@@ -2842,16 +2850,16 @@
         <v/>
       </c>
       <c r="M17" s="7" t="n">
-        <v>46226</v>
+        <v>46240</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>90 days</t>
+          <t>120 days</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>OPTUM</t>
+          <t>TRIWEST</t>
         </is>
       </c>
       <c r="P17" s="6" t="n"/>
@@ -2861,7 +2869,7 @@
         <v>1</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U17" s="8" t="n">
         <v>0</v>
@@ -2869,20 +2877,16 @@
       <c r="V17" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W17" s="6" t="inlineStr">
-        <is>
-          <t>05/25/2026</t>
-        </is>
-      </c>
+      <c r="W17" s="6" t="n"/>
       <c r="X17" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="Y17" s="5" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="Z17" s="6" t="inlineStr">
         <is>
-          <t>F4323</t>
+          <t>F39</t>
         </is>
       </c>
       <c r="AA17" s="6" t="n"/>
@@ -2891,7 +2895,7 @@
       <c r="AD17" s="5" t="n"/>
       <c r="AE17" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF17" s="6" t="inlineStr">
@@ -2909,9 +2913,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI17" s="9" t="n"/>
+      <c r="AI17" s="9" t="inlineStr">
+        <is>
+          <t>This payer name is on 2 carrier rows in the reference (VETERANS ADMIN (VA CCN) 180 days, and TRIWEST 120 days). The shorter TRIWEST window is applied - confirm which programme the claim belongs to before relying on the longer one.</t>
+        </is>
+      </c>
       <c r="AJ17" s="5" t="n">
-        <v>640</v>
+        <v>777</v>
       </c>
     </row>
     <row r="18">
@@ -2919,26 +2927,26 @@
       <c r="B18" s="3" t="n"/>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="5" t="n">
-        <v>557132196</v>
+        <v>555379100</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>HF460603685</t>
+          <t>HF549150041</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>04/24/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -2948,7 +2956,7 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K18" s="4" t="n"/>
@@ -2957,16 +2965,16 @@
         <v/>
       </c>
       <c r="M18" s="7" t="n">
-        <v>46226</v>
+        <v>46240</v>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>90 days</t>
+          <t>120 days</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>OPTUM</t>
+          <t>TRIWEST</t>
         </is>
       </c>
       <c r="P18" s="6" t="n"/>
@@ -2976,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="T18" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U18" s="8" t="n">
         <v>0</v>
@@ -2984,20 +2992,16 @@
       <c r="V18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W18" s="6" t="inlineStr">
-        <is>
-          <t>05/25/2026</t>
-        </is>
-      </c>
+      <c r="W18" s="6" t="n"/>
       <c r="X18" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="Y18" s="5" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="Z18" s="6" t="inlineStr">
         <is>
-          <t>F4323</t>
+          <t>F39</t>
         </is>
       </c>
       <c r="AA18" s="6" t="n"/>
@@ -3006,7 +3010,7 @@
       <c r="AD18" s="5" t="n"/>
       <c r="AE18" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF18" s="6" t="inlineStr">
@@ -3024,9 +3028,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI18" s="9" t="n"/>
+      <c r="AI18" s="9" t="inlineStr">
+        <is>
+          <t>This payer name is on 2 carrier rows in the reference (VETERANS ADMIN (VA CCN) 180 days, and TRIWEST 120 days). The shorter TRIWEST window is applied - confirm which programme the claim belongs to before relying on the longer one.</t>
+        </is>
+      </c>
       <c r="AJ18" s="5" t="n">
-        <v>674</v>
+        <v>778</v>
       </c>
     </row>
     <row r="19">
@@ -3657,16 +3665,16 @@
         <v/>
       </c>
       <c r="M2" s="7" t="n">
-        <v>46320</v>
+        <v>46260</v>
       </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
-          <t>180 days</t>
+          <t>120 days</t>
         </is>
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
-          <t>VETERANS ADMIN (VA CCN)</t>
+          <t>TRIWEST</t>
         </is>
       </c>
       <c r="P2" s="6" t="inlineStr">
@@ -3736,7 +3744,11 @@
           <t>DME</t>
         </is>
       </c>
-      <c r="AI2" s="9" t="n"/>
+      <c r="AI2" s="9" t="inlineStr">
+        <is>
+          <t>This payer name is on 2 carrier rows in the reference (VETERANS ADMIN (VA CCN) 180 days, and TRIWEST 120 days). The shorter TRIWEST window is applied - confirm which programme the claim belongs to before relying on the longer one.</t>
+        </is>
+      </c>
       <c r="AJ2" s="5" t="n">
         <v>854</v>
       </c>
@@ -5311,7 +5323,11 @@
           <t>DME</t>
         </is>
       </c>
-      <c r="AI15" s="9" t="n"/>
+      <c r="AI15" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ15" s="5" t="n">
         <v>779</v>
       </c>
@@ -5797,7 +5813,7 @@
       </c>
       <c r="AI19" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ19" s="5" t="n">
@@ -7134,7 +7150,7 @@
       </c>
       <c r="AI30" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ30" s="5" t="n">
@@ -7388,7 +7404,7 @@
       </c>
       <c r="AI32" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ32" s="5" t="n">
@@ -8053,11 +8069,11 @@
         <v/>
       </c>
       <c r="M2" s="7" t="n">
-        <v>46346</v>
+        <v>46312</v>
       </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
-          <t>7 months</t>
+          <t>180 days</t>
         </is>
       </c>
       <c r="O2" s="6" t="inlineStr">
@@ -8142,7 +8158,7 @@
       </c>
       <c r="AI2" s="9" t="inlineStr">
         <is>
-          <t>7 months because Health Choice is the primary payer here (6 months when it is not). Counted in calendar months.</t>
+          <t>Limit as stated: 6 months (not primary) or 7 months (primary). The reference converts months at 30 days, so the real deadline may fall a few days later - count calendar months where it matters.</t>
         </is>
       </c>
       <c r="AJ2" s="5" t="n">
@@ -8192,11 +8208,11 @@
         <v/>
       </c>
       <c r="M3" s="7" t="n">
-        <v>46346</v>
+        <v>46312</v>
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>7 months</t>
+          <t>180 days</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
@@ -8273,7 +8289,7 @@
       </c>
       <c r="AI3" s="9" t="inlineStr">
         <is>
-          <t>7 months because Health Choice is the primary payer here (6 months when it is not). Counted in calendar months.</t>
+          <t>Limit as stated: 6 months (not primary) or 7 months (primary). The reference converts months at 30 days, so the real deadline may fall a few days later - count calendar months where it matters.</t>
         </is>
       </c>
       <c r="AJ3" s="5" t="n">
@@ -8323,11 +8339,11 @@
         <v/>
       </c>
       <c r="M4" s="7" t="n">
-        <v>46346</v>
+        <v>46312</v>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>7 months</t>
+          <t>180 days</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
@@ -8408,7 +8424,7 @@
       </c>
       <c r="AI4" s="9" t="inlineStr">
         <is>
-          <t>7 months because Health Choice is the primary payer here (6 months when it is not). Counted in calendar months.</t>
+          <t>Limit as stated: 6 months (not primary) or 7 months (primary). The reference converts months at 30 days, so the real deadline may fall a few days later - count calendar months where it matters.</t>
         </is>
       </c>
       <c r="AJ4" s="5" t="n">
@@ -9440,7 +9456,7 @@
       </c>
       <c r="AI12" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ12" s="5" t="n">
@@ -9579,7 +9595,7 @@
       </c>
       <c r="AI13" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ13" s="5" t="n">
@@ -9714,7 +9730,7 @@
       </c>
       <c r="AI14" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ14" s="5" t="n">
@@ -9847,7 +9863,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI15" s="9" t="n"/>
+      <c r="AI15" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ15" s="5" t="n">
         <v>273</v>
       </c>
@@ -9974,7 +9994,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI16" s="9" t="n"/>
+      <c r="AI16" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ16" s="5" t="n">
         <v>274</v>
       </c>
@@ -10101,7 +10125,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI17" s="9" t="n"/>
+      <c r="AI17" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ17" s="5" t="n">
         <v>275</v>
       </c>
@@ -10232,7 +10260,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI18" s="9" t="n"/>
+      <c r="AI18" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ18" s="5" t="n">
         <v>276</v>
       </c>
@@ -10365,7 +10397,7 @@
       </c>
       <c r="AI19" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ19" s="5" t="n">
@@ -10492,7 +10524,7 @@
       </c>
       <c r="AI20" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ20" s="5" t="n">
@@ -10619,7 +10651,7 @@
       </c>
       <c r="AI21" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ21" s="5" t="n">
@@ -10750,7 +10782,7 @@
       </c>
       <c r="AI22" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ22" s="5" t="n">
@@ -10881,7 +10913,7 @@
       </c>
       <c r="AI23" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ23" s="5" t="n">
@@ -11016,7 +11048,7 @@
       </c>
       <c r="AI24" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
@@ -11147,7 +11179,7 @@
       </c>
       <c r="AI25" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ25" s="5" t="n">
@@ -11288,7 +11320,7 @@
       </c>
       <c r="AI26" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ26" s="5" t="n">
@@ -11429,7 +11461,7 @@
       </c>
       <c r="AI27" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ27" s="5" t="n">
@@ -11566,7 +11598,7 @@
       </c>
       <c r="AI28" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ28" s="5" t="n">
@@ -11703,7 +11735,7 @@
       </c>
       <c r="AI29" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ29" s="5" t="n">
@@ -11840,7 +11872,7 @@
       </c>
       <c r="AI30" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ30" s="5" t="n">
@@ -11973,7 +12005,7 @@
       </c>
       <c r="AI31" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ31" s="5" t="n">
@@ -12118,7 +12150,7 @@
       </c>
       <c r="AI32" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ32" s="5" t="n">
@@ -14604,7 +14636,7 @@
       </c>
       <c r="AI12" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ12" s="5" t="n">
@@ -15463,7 +15495,11 @@
           <t>ORTHO</t>
         </is>
       </c>
-      <c r="AI19" s="9" t="n"/>
+      <c r="AI19" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ19" s="5" t="n">
         <v>108</v>
       </c>
@@ -15814,7 +15850,7 @@
       </c>
       <c r="AI22" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ22" s="5" t="n">
@@ -15937,7 +15973,7 @@
       </c>
       <c r="AI23" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ23" s="5" t="n">
@@ -16064,7 +16100,7 @@
       </c>
       <c r="AI24" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
@@ -16191,7 +16227,7 @@
       </c>
       <c r="AI25" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ25" s="5" t="n">
@@ -17564,7 +17600,7 @@
       </c>
       <c r="AI36" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ36" s="5" t="n">
@@ -18564,7 +18600,7 @@
       </c>
       <c r="AI3" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ3" s="5" t="n">
@@ -20980,7 +21016,7 @@
       </c>
       <c r="AI23" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ23" s="5" t="n">
@@ -21099,7 +21135,7 @@
       </c>
       <c r="AI24" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
@@ -22783,7 +22819,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI38" s="9" t="n"/>
+      <c r="AI38" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ38" s="5" t="n">
         <v>790</v>
       </c>
@@ -22881,21 +22921,21 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2 - Due in 6-30 days: 3</t>
+          <t xml:space="preserve">    2 - Due in 6-30 days: 4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3 - Due in 31+ days: 49</t>
+          <t xml:space="preserve">    3 - Due in 31+ days: 46</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4 - Past deadline: 98</t>
+          <t xml:space="preserve">    4 - Past deadline: 100</t>
         </is>
       </c>
     </row>

--- a/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
@@ -27,10 +27,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="MM/DD/YYYY"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -127,7 +126,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -282,12 +281,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -332,12 +331,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -382,12 +381,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -432,12 +431,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -482,12 +481,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -22864,7 +22863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -23004,7 +23003,7 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "25/06/2026";  Date Worked 1: "12/08/2026".</t>
+          <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Date Worked 1: "08/12/2026".</t>
         </is>
       </c>
     </row>
@@ -23021,46 +23020,39 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Both are real dates displayed DD/MM/YYYY. Processed Date is already filled in on the 13 claim lines whose Notes recorded one - the Note still carries the original wording, so nothing was lost. Date Worked 1 starts empty.</t>
+          <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Processed Date is already filled in on the 13 claim lines whose Notes recorded one - the Note still carries the original wording, so nothing was lost. Date Worked 1 starts empty.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Careful when typing into them: Excel reads what you type using its own date setting, not the DD/MM/YYYY the cell displays. On a US Excel, typing 06/25/2026 gives 25 June and the cell then shows 25/06/2026. Type the date the way your Excel expects it and let the cell do the formatting, or check the formula bar afterwards. Every other date column in these files is MM/DD/YYYY, as in the source data.</t>
-        </is>
-      </c>
+      <c r="A26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr"/>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>How this file feeds the master</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>How this file feeds the master</t>
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 1,086 claim lines for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 1,086 claim lines for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+          <t>The link is matched on Line ID (last column), not on row position, so sorting and filtering these sheets is safe. Do not edit or delete the Line ID column, and do not rename the specialty sheet tabs.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>The link is matched on Line ID (last column), not on row position, so sorting and filtering these sheets is safe. Do not edit or delete the Line ID column, and do not rename the specialty sheet tabs.</t>
-        </is>
-      </c>
+      <c r="A30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Everything else in this file is a static copy of the source data from 'Specialty Claims Pending 2026-S1.xlsx' (sheet 'Merged').</t>
         </is>
